--- a/Projects/Pistons_Players_Regular_Season_Data_2024-2025.xlsx
+++ b/Projects/Pistons_Players_Regular_Season_Data_2024-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B31D9FA-54C5-534D-BBC8-2EF8D2C15D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609354DD-8863-7A46-9CC3-D9ACBEB3EB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17560" activeTab="1" xr2:uid="{9F5AD747-0CA0-0449-80A8-FFDBC90AA643}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17560" activeTab="9" xr2:uid="{9F5AD747-0CA0-0449-80A8-FFDBC90AA643}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="Per 100 Poss" sheetId="5" r:id="rId5"/>
     <sheet name="Advanced" sheetId="6" r:id="rId6"/>
     <sheet name="Advanced Shooting" sheetId="7" r:id="rId7"/>
+    <sheet name="Shooting" sheetId="8" r:id="rId8"/>
+    <sheet name="Play-by-Play" sheetId="9" r:id="rId9"/>
+    <sheet name="Salaries" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="170">
   <si>
     <t>No.</t>
   </si>
@@ -619,12 +622,147 @@
   <si>
     <t>Added_TS Add</t>
   </si>
+  <si>
+    <t>Dist.</t>
+  </si>
+  <si>
+    <t>2P_% of FGA by Distance</t>
+  </si>
+  <si>
+    <t>0-3_% of FGA by Distance</t>
+  </si>
+  <si>
+    <t>3-10_% of FGA by Distance</t>
+  </si>
+  <si>
+    <t>10-16_% of FGA by Distance</t>
+  </si>
+  <si>
+    <t>16-3P_% of FGA by Distance</t>
+  </si>
+  <si>
+    <t>3P_% of FGA by Distance</t>
+  </si>
+  <si>
+    <t>2P_FG% by Distance</t>
+  </si>
+  <si>
+    <t>0-3_FG% by Distance</t>
+  </si>
+  <si>
+    <t>3-10_FG% by Distance</t>
+  </si>
+  <si>
+    <t>10-16_FG% by Distance</t>
+  </si>
+  <si>
+    <t>16-3P_FG% by Distance</t>
+  </si>
+  <si>
+    <t>3P_FG% by Distance</t>
+  </si>
+  <si>
+    <t>2P_% of FG Ast'd</t>
+  </si>
+  <si>
+    <t>3P_% of FG Ast'd</t>
+  </si>
+  <si>
+    <t>%FGA_Dunks</t>
+  </si>
+  <si>
+    <t>#_Dunks</t>
+  </si>
+  <si>
+    <t>%3PA_Corner_3s</t>
+  </si>
+  <si>
+    <t>3P%_Corner_3s</t>
+  </si>
+  <si>
+    <t>Att._1/2_Court</t>
+  </si>
+  <si>
+    <t>Md._1/2_Court</t>
+  </si>
+  <si>
+    <t>And1</t>
+  </si>
+  <si>
+    <t>PG%_Position Estimate</t>
+  </si>
+  <si>
+    <t>SG%_Position Estimate</t>
+  </si>
+  <si>
+    <t>SF%_Position Estimate</t>
+  </si>
+  <si>
+    <t>PF%_Position Estimate</t>
+  </si>
+  <si>
+    <t>C%_Position Estimate</t>
+  </si>
+  <si>
+    <t>OnCourt_+/- Per 100 Poss</t>
+  </si>
+  <si>
+    <t>On-Off_+/- Per 100 Poss</t>
+  </si>
+  <si>
+    <t>BadPass_Turnovers</t>
+  </si>
+  <si>
+    <t>LostBall_Turnovers</t>
+  </si>
+  <si>
+    <t>Shoot_Fouls Committed</t>
+  </si>
+  <si>
+    <t>Off._Fouls Committed</t>
+  </si>
+  <si>
+    <t>Shoot_Fouls Drawn</t>
+  </si>
+  <si>
+    <t>Off._Fouls Drawn</t>
+  </si>
+  <si>
+    <t>PGA (Points Generated Off Assists)</t>
+  </si>
+  <si>
+    <t>Blkd (Field Goal Attempts that were Blocked)</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Tim Hardaway</t>
+  </si>
+  <si>
+    <t>Dewayne Dedmon</t>
+  </si>
+  <si>
+    <t>Wendell Moore</t>
+  </si>
+  <si>
+    <t>Lindy Waters</t>
+  </si>
+  <si>
+    <t>Javante McCoy</t>
+  </si>
+  <si>
+    <t>Ron Harper</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -672,6 +810,18 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9.4"/>
+      <color rgb="FF008800"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.4"/>
+      <color rgb="FFCC0000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -694,7 +844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -704,6 +854,10 @@
     <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1724,6 +1878,312 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7B0108E-8412-2E40-8E22-0BA5B2C27DF7}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="12">
+        <v>25365854</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="12">
+        <v>16193183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="12">
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="12">
+        <v>13940809</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="12">
+        <v>13025250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="12">
+        <v>8376000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="12">
+        <v>8245320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="12">
+        <v>7977240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="12">
+        <v>7692308</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="12">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="12">
+        <v>4536840</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="12">
+        <v>2755080</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C14" s="12">
+        <v>2748674</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" s="12">
+        <v>2537040</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="12">
+        <v>2485563</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="12">
+        <v>2196970</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1427671</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="12">
+        <v>1257153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="12">
+        <v>47265</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.basketball-reference.com/players/h/harrito02.html" xr:uid="{270E11AD-43AF-3446-8EA3-7F53B1E2A255}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.basketball-reference.com/players/h/hardati02.html" xr:uid="{168012CE-EAC1-1841-A046-257EE6F7A4BA}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://www.basketball-reference.com/players/s/stewais01.html" xr:uid="{23AC7A1B-FEC4-C343-AD2A-A2EE14B54AC9}"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://www.basketball-reference.com/players/c/cunnica01.html" xr:uid="{1F95076F-E2FF-1840-81CD-9FFFDFBFAA0D}"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://www.basketball-reference.com/players/s/schrode01.html" xr:uid="{11048B02-C8B5-C046-8929-5D5BF69A5892}"/>
+    <hyperlink ref="B7" r:id="rId6" display="https://www.basketball-reference.com/players/t/thompau01.html" xr:uid="{B42363A6-515D-0148-998F-644769463056}"/>
+    <hyperlink ref="B8" r:id="rId7" display="https://www.basketball-reference.com/players/h/hollaro01.html" xr:uid="{0385846C-6A4A-374F-90D0-D1C5E21812C3}"/>
+    <hyperlink ref="B9" r:id="rId8" display="https://www.basketball-reference.com/players/i/iveyja01.html" xr:uid="{AED6F3D3-B461-094C-9C98-320B2AE17228}"/>
+    <hyperlink ref="B10" r:id="rId9" display="https://www.basketball-reference.com/players/f/fontesi01.html" xr:uid="{CAD0527C-068F-844D-9BA6-02AC60747BBE}"/>
+    <hyperlink ref="B11" r:id="rId10" display="https://www.basketball-reference.com/players/b/beaslma01.html" xr:uid="{0D64CA21-7987-1244-A3B4-43BCE85F1782}"/>
+    <hyperlink ref="B12" r:id="rId11" display="https://www.basketball-reference.com/players/d/durenja01.html" xr:uid="{BC370232-1A1D-B44A-9AD1-C7F799B33C69}"/>
+    <hyperlink ref="B13" r:id="rId12" display="https://www.basketball-reference.com/players/s/sassema01.html" xr:uid="{0C4B51EE-D356-6345-9E54-84ED9A8E400B}"/>
+    <hyperlink ref="B14" r:id="rId13" display="https://www.basketball-reference.com/players/d/dedmode01.html" xr:uid="{1BE85681-241E-4B42-841F-AC8783CBAF02}"/>
+    <hyperlink ref="B15" r:id="rId14" display="https://www.basketball-reference.com/players/m/moorewe01.html" xr:uid="{E36ACE00-D4B7-664D-9DAF-E9E820FB8F50}"/>
+    <hyperlink ref="B16" r:id="rId15" display="https://www.basketball-reference.com/players/r/reedpa01.html" xr:uid="{46A10F3E-E000-8045-B52B-BEA2B11AD881}"/>
+    <hyperlink ref="B17" r:id="rId16" display="https://www.basketball-reference.com/players/w/waterli01.html" xr:uid="{F1707DA9-0B39-6140-86B0-578AFCE52FB3}"/>
+    <hyperlink ref="B18" r:id="rId17" display="https://www.basketball-reference.com/players/r/reedpa01.html" xr:uid="{6DF20458-B972-014D-AA40-B9A495DC180B}"/>
+    <hyperlink ref="B19" r:id="rId18" display="https://www.basketball-reference.com/players/k/klintbo01.html" xr:uid="{196D9626-A6BA-6F41-9C15-2A6B874F08F2}"/>
+    <hyperlink ref="B20" r:id="rId19" display="https://www.basketball-reference.com/players/m/mccoyja01.html" xr:uid="{233E59DC-7EA2-B543-88CD-C4C2AF949190}"/>
+    <hyperlink ref="B21" r:id="rId20" display="https://www.basketball-reference.com/players/j/jenkida01.html" xr:uid="{901ED111-30FE-724C-A8C1-D9CEF3B5D204}"/>
+    <hyperlink ref="B22" r:id="rId21" display="https://www.basketball-reference.com/players/s/swideco01.html" xr:uid="{65A55A51-9686-2748-B9B9-D99C4857A277}"/>
+    <hyperlink ref="B23" r:id="rId22" display="https://www.basketball-reference.com/players/w/willial06.html" xr:uid="{A8CC2C0F-6B8E-154D-B8B5-EA35D2336281}"/>
+    <hyperlink ref="B24" r:id="rId23" display="https://www.basketball-reference.com/players/s/smithto05.html" xr:uid="{CC06FBD2-1D8D-AC4F-8F5C-17631BEF894E}"/>
+    <hyperlink ref="B25" r:id="rId24" display="https://www.basketball-reference.com/players/h/harpero02.html" xr:uid="{E2F9273B-532D-8848-965B-9CC24327E5B7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DB2531-B10A-8044-8961-4025511EEEA0}">
   <dimension ref="A1:AD22"/>
@@ -13607,4 +14067,3646 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E68F7E6-2BB9-9C45-B81B-547F6AA4EA2F}">
+  <dimension ref="A1:AD22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>70</v>
+      </c>
+      <c r="F2" s="2">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2452</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="I2" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0.129</v>
+      </c>
+      <c r="N2" s="2">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0.497</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="V2" s="2">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="X2" s="2">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>4</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2">
+        <v>73</v>
+      </c>
+      <c r="F3" s="2">
+        <v>73</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2305</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="I3" s="2">
+        <v>13.1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="N3" s="2">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0.77</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0.314</v>
+      </c>
+      <c r="U3" s="2">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="V3" s="2">
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="X3" s="2">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>56</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="2"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8">
+        <v>82</v>
+      </c>
+      <c r="F4" s="2">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2283</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.43</v>
+      </c>
+      <c r="I4" s="2">
+        <v>20.8</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="M4" s="2">
+        <v>5.5E-2</v>
+      </c>
+      <c r="N4" s="2">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0.93700000000000006</v>
+      </c>
+      <c r="X4" s="2">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2">
+        <v>77</v>
+      </c>
+      <c r="F5" s="2">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2153</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="I5" s="2">
+        <v>20.2</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="K5" s="2">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="M5" s="2">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="N5" s="2">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="P5" s="2">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="V5" s="2">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="W5" s="2">
+        <v>0.92300000000000004</v>
+      </c>
+      <c r="X5" s="2">
+        <v>1.6E-2</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>8</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>0.373</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="2"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2">
+        <v>78</v>
+      </c>
+      <c r="F6" s="2">
+        <v>78</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2034</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="I6" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="M6" s="2">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="N6" s="2">
+        <v>2E-3</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0.76</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T6" s="2">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2">
+        <v>0.624</v>
+      </c>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2">
+        <v>0.441</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>219</v>
+      </c>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2">
+        <v>72</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1434</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.438</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="M7" s="2">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="N7" s="2">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0.73</v>
+      </c>
+      <c r="W7" s="2">
+        <v>1</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0.111</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="2">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2">
+        <v>59</v>
+      </c>
+      <c r="F8" s="2">
+        <v>48</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1328</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0.498</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="M8" s="2">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0.107</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0.57199999999999995</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0.69</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.224</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0.621</v>
+      </c>
+      <c r="W8" s="2">
+        <v>1</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>107</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0.51</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="2"/>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2">
+        <v>81</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1266</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="I9" s="2">
+        <v>12.1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="M9" s="2">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="N9" s="2">
+        <v>1.4E-2</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="W9" s="2">
+        <v>1</v>
+      </c>
+      <c r="X9" s="2">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="2"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2">
+        <v>75</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1237</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="I10" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="M10" s="2">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="N10" s="2">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.623</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="V10" s="2">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="W10" s="2">
+        <v>1</v>
+      </c>
+      <c r="X10" s="2">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>11</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2"/>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2">
+        <v>30</v>
+      </c>
+      <c r="F11" s="2">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2">
+        <v>898</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="I11" s="2">
+        <v>13.7</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.627</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0.245</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0.245</v>
+      </c>
+      <c r="M11" s="2">
+        <v>9.4E-2</v>
+      </c>
+      <c r="N11" s="2">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0.373</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="W11" s="2">
+        <v>0.746</v>
+      </c>
+      <c r="X11" s="2">
+        <v>2.4E-2</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>9</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="2"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2">
+        <v>57</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>811</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="I12" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.128</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0.155</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="N12" s="2">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0.435</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0.44</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="V12" s="2">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0.151</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="2"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2">
+        <v>28</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2">
+        <v>705</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.378</v>
+      </c>
+      <c r="I13" s="2">
+        <v>16</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0.155</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="N13" s="2">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0.434</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0.59</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0.42399999999999999</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0.182</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="V13" s="2">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="W13" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>0.113</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="2"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>438</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="I14" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.80300000000000005</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.35899999999999999</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0.254</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0.155</v>
+      </c>
+      <c r="N14" s="2">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0.318</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="W14" s="2">
+        <v>1</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="2"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2">
+        <v>23</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>219</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0.46</v>
+      </c>
+      <c r="I15" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.72</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="W15" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="2"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="2">
+        <v>27</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>123</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="I16" s="2">
+        <v>23.2</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="K16" s="2">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <v>2.3E-2</v>
+      </c>
+      <c r="N16" s="2">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2">
+        <v>1</v>
+      </c>
+      <c r="T16" s="2">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="V16" s="2">
+        <v>1</v>
+      </c>
+      <c r="W16" s="2">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="X16" s="2">
+        <v>2.3E-2</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="2"/>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2">
+        <v>21</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="2">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>42</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I17" s="2">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>1</v>
+      </c>
+      <c r="R17" s="2">
+        <v>1</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="V17" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="W17" s="2">
+        <v>1</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="2"/>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2">
+        <v>23</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2">
+        <v>7</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="I18" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="V18" s="2">
+        <v>0</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="2"/>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2">
+        <v>24</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>22</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0.111</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="2"/>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2">
+        <v>24</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>17</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="I20" s="2">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2">
+        <v>1</v>
+      </c>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2">
+        <v>1</v>
+      </c>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="2"/>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="2">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>25.4</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="2"/>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2">
+        <v>25</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>4</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="P22" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>1</v>
+      </c>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2">
+        <v>1</v>
+      </c>
+      <c r="X22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.basketball-reference.com/players/c/cunnica01.html" xr:uid="{3B05E8D8-8ED8-2446-8087-A9C35335C16E}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.basketball-reference.com/players/h/harrito02.html" xr:uid="{48D283DE-D567-414A-B832-C60DED6A7A04}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://www.basketball-reference.com/players/b/beaslma01.html" xr:uid="{0EDB77B7-EB51-D745-98EC-3E35FEAF6E23}"/>
+    <hyperlink ref="AD4" r:id="rId4" location="all_smoy" display="https://www.basketball-reference.com/awards/awards_2025.html - all_smoy" xr:uid="{04A1AC4F-D0E8-CE44-9CFD-FABD059885F6}"/>
+    <hyperlink ref="B5" r:id="rId5" display="https://www.basketball-reference.com/players/h/hardati02.html" xr:uid="{45E993A9-BFBB-0540-AFA4-121A9063873C}"/>
+    <hyperlink ref="B6" r:id="rId6" display="https://www.basketball-reference.com/players/d/durenja01.html" xr:uid="{4FF6F745-D056-424A-A5BF-1C9DCE905BE3}"/>
+    <hyperlink ref="B7" r:id="rId7" display="https://www.basketball-reference.com/players/s/stewais01.html" xr:uid="{781AA92B-3445-1A4F-B6AC-998A32293982}"/>
+    <hyperlink ref="B8" r:id="rId8" display="https://www.basketball-reference.com/players/t/thompau01.html" xr:uid="{22FA13F9-92C2-B14B-85D0-5F23B2B91DA5}"/>
+    <hyperlink ref="B9" r:id="rId9" display="https://www.basketball-reference.com/players/h/hollaro01.html" xr:uid="{A9A1D19F-A5D7-CC4C-8C94-9BBB045BF609}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://www.basketball-reference.com/players/f/fontesi01.html" xr:uid="{36AAB230-9AFB-5944-B656-06ACF1D9A9C8}"/>
+    <hyperlink ref="B11" r:id="rId11" display="https://www.basketball-reference.com/players/i/iveyja01.html" xr:uid="{B92648A1-1AAC-FB4B-9D00-56D4415768B4}"/>
+    <hyperlink ref="B12" r:id="rId12" display="https://www.basketball-reference.com/players/s/sassema01.html" xr:uid="{EEFDDCE7-0D70-6940-87B9-1985A222C00B}"/>
+    <hyperlink ref="B13" r:id="rId13" display="https://www.basketball-reference.com/players/s/schrode01.html" xr:uid="{1D439C42-094F-994A-BB3F-5AF50E3F66ED}"/>
+    <hyperlink ref="B14" r:id="rId14" display="https://www.basketball-reference.com/players/r/reedpa01.html" xr:uid="{A978BA15-E659-314A-AB63-0BFCC80DC630}"/>
+    <hyperlink ref="B15" r:id="rId15" display="https://www.basketball-reference.com/players/m/moorewe01.html" xr:uid="{365945FB-D909-5A48-9A90-1960087A0827}"/>
+    <hyperlink ref="B16" r:id="rId16" display="https://www.basketball-reference.com/players/w/waterli01.html" xr:uid="{ABFCCEB0-4314-234E-8343-BDE5046A0309}"/>
+    <hyperlink ref="B17" r:id="rId17" display="https://www.basketball-reference.com/players/k/klintbo01.html" xr:uid="{8C881CB4-C5D3-DD43-A441-5EBF287FAF78}"/>
+    <hyperlink ref="B18" r:id="rId18" display="https://www.basketball-reference.com/players/j/jenkida01.html" xr:uid="{1729C31C-ECE0-2B47-8211-D5EC9CE645CF}"/>
+    <hyperlink ref="B19" r:id="rId19" display="https://www.basketball-reference.com/players/s/smithto05.html" xr:uid="{850C4430-3548-DC4B-9066-6D783FA8201C}"/>
+    <hyperlink ref="B20" r:id="rId20" display="https://www.basketball-reference.com/players/h/harpero02.html" xr:uid="{CEFE1D52-E261-AE4A-9246-CC7842A477E0}"/>
+    <hyperlink ref="B21" r:id="rId21" display="https://www.basketball-reference.com/players/s/swideco01.html" xr:uid="{6534F2CF-EF5F-374B-96B5-539E606E6708}"/>
+    <hyperlink ref="B22" r:id="rId22" display="https://www.basketball-reference.com/players/w/willial06.html" xr:uid="{DFAFC8D9-BAE9-964E-B973-08776A2FBB1B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC88E3D5-5E3F-594A-83A2-9F9C1045A378}">
+  <dimension ref="A1:X22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>70</v>
+      </c>
+      <c r="F2" s="2">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2452</v>
+      </c>
+      <c r="H2" s="2">
+        <v>84</v>
+      </c>
+      <c r="I2" s="2">
+        <v>16</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="10">
+        <v>3.4</v>
+      </c>
+      <c r="N2" s="10">
+        <v>3.7</v>
+      </c>
+      <c r="O2" s="2">
+        <v>173</v>
+      </c>
+      <c r="P2" s="2">
+        <v>105</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>87</v>
+      </c>
+      <c r="R2" s="2">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2">
+        <v>165</v>
+      </c>
+      <c r="T2" s="2">
+        <v>6</v>
+      </c>
+      <c r="U2" s="2">
+        <v>1511</v>
+      </c>
+      <c r="V2" s="2">
+        <v>39</v>
+      </c>
+      <c r="W2" s="2">
+        <v>100</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2">
+        <v>73</v>
+      </c>
+      <c r="F3" s="2">
+        <v>73</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2305</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2">
+        <v>98</v>
+      </c>
+      <c r="L3" s="2">
+        <v>2</v>
+      </c>
+      <c r="M3" s="10">
+        <v>3.7</v>
+      </c>
+      <c r="N3" s="10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O3" s="2">
+        <v>29</v>
+      </c>
+      <c r="P3" s="2">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>89</v>
+      </c>
+      <c r="R3" s="2">
+        <v>15</v>
+      </c>
+      <c r="S3" s="2">
+        <v>84</v>
+      </c>
+      <c r="T3" s="2">
+        <v>4</v>
+      </c>
+      <c r="U3" s="2">
+        <v>396</v>
+      </c>
+      <c r="V3" s="2">
+        <v>20</v>
+      </c>
+      <c r="W3" s="2">
+        <v>46</v>
+      </c>
+      <c r="X3" s="2"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8">
+        <v>82</v>
+      </c>
+      <c r="F4" s="2">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2283</v>
+      </c>
+      <c r="H4" s="2">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2">
+        <v>75</v>
+      </c>
+      <c r="J4" s="2">
+        <v>10</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="N4" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="O4" s="2">
+        <v>44</v>
+      </c>
+      <c r="P4" s="2">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>61</v>
+      </c>
+      <c r="R4" s="2">
+        <v>6</v>
+      </c>
+      <c r="S4" s="2">
+        <v>53</v>
+      </c>
+      <c r="T4" s="2">
+        <v>8</v>
+      </c>
+      <c r="U4" s="2">
+        <v>332</v>
+      </c>
+      <c r="V4" s="2">
+        <v>14</v>
+      </c>
+      <c r="W4" s="2">
+        <v>29</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2">
+        <v>77</v>
+      </c>
+      <c r="F5" s="2">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2153</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>42</v>
+      </c>
+      <c r="J5" s="2">
+        <v>56</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="11">
+        <v>-4.3</v>
+      </c>
+      <c r="O5" s="2">
+        <v>27</v>
+      </c>
+      <c r="P5" s="2">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>49</v>
+      </c>
+      <c r="R5" s="2">
+        <v>4</v>
+      </c>
+      <c r="S5" s="2">
+        <v>57</v>
+      </c>
+      <c r="T5" s="2">
+        <v>41</v>
+      </c>
+      <c r="U5" s="2">
+        <v>292</v>
+      </c>
+      <c r="V5" s="2">
+        <v>16</v>
+      </c>
+      <c r="W5" s="2">
+        <v>19</v>
+      </c>
+      <c r="X5" s="2"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2">
+        <v>78</v>
+      </c>
+      <c r="F6" s="2">
+        <v>78</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2034</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>100</v>
+      </c>
+      <c r="M6" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N6" s="11">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="O6" s="2">
+        <v>71</v>
+      </c>
+      <c r="P6" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>148</v>
+      </c>
+      <c r="R6" s="2">
+        <v>30</v>
+      </c>
+      <c r="S6" s="2">
+        <v>119</v>
+      </c>
+      <c r="T6" s="2">
+        <v>2</v>
+      </c>
+      <c r="U6" s="2">
+        <v>480</v>
+      </c>
+      <c r="V6" s="2">
+        <v>28</v>
+      </c>
+      <c r="W6" s="2">
+        <v>55</v>
+      </c>
+      <c r="X6" s="2"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2">
+        <v>72</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1434</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
+        <v>99</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="N7" s="11">
+        <v>-2.1</v>
+      </c>
+      <c r="O7" s="2">
+        <v>19</v>
+      </c>
+      <c r="P7" s="2">
+        <v>14</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>85</v>
+      </c>
+      <c r="R7" s="2">
+        <v>25</v>
+      </c>
+      <c r="S7" s="2">
+        <v>40</v>
+      </c>
+      <c r="T7" s="2">
+        <v>4</v>
+      </c>
+      <c r="U7" s="2">
+        <v>310</v>
+      </c>
+      <c r="V7" s="2">
+        <v>11</v>
+      </c>
+      <c r="W7" s="2">
+        <v>12</v>
+      </c>
+      <c r="X7" s="2"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="2">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2">
+        <v>59</v>
+      </c>
+      <c r="F8" s="2">
+        <v>48</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1328</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2">
+        <v>75</v>
+      </c>
+      <c r="K8" s="2">
+        <v>23</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="N8" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="O8" s="2">
+        <v>38</v>
+      </c>
+      <c r="P8" s="2">
+        <v>28</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>58</v>
+      </c>
+      <c r="R8" s="2">
+        <v>8</v>
+      </c>
+      <c r="S8" s="2">
+        <v>62</v>
+      </c>
+      <c r="T8" s="2">
+        <v>21</v>
+      </c>
+      <c r="U8" s="2">
+        <v>330</v>
+      </c>
+      <c r="V8" s="2">
+        <v>9</v>
+      </c>
+      <c r="W8" s="2">
+        <v>42</v>
+      </c>
+      <c r="X8" s="2"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2">
+        <v>81</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1266</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>2</v>
+      </c>
+      <c r="J9" s="2">
+        <v>75</v>
+      </c>
+      <c r="K9" s="2">
+        <v>23</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11">
+        <v>-1</v>
+      </c>
+      <c r="N9" s="11">
+        <v>-4.4000000000000004</v>
+      </c>
+      <c r="O9" s="2">
+        <v>26</v>
+      </c>
+      <c r="P9" s="2">
+        <v>29</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>67</v>
+      </c>
+      <c r="R9" s="2">
+        <v>8</v>
+      </c>
+      <c r="S9" s="2">
+        <v>66</v>
+      </c>
+      <c r="T9" s="2">
+        <v>13</v>
+      </c>
+      <c r="U9" s="2">
+        <v>208</v>
+      </c>
+      <c r="V9" s="2">
+        <v>18</v>
+      </c>
+      <c r="W9" s="2">
+        <v>23</v>
+      </c>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2">
+        <v>75</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1237</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>22</v>
+      </c>
+      <c r="K10" s="2">
+        <v>77</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1</v>
+      </c>
+      <c r="M10" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="N10" s="11">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="O10" s="2">
+        <v>25</v>
+      </c>
+      <c r="P10" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>52</v>
+      </c>
+      <c r="R10" s="2">
+        <v>2</v>
+      </c>
+      <c r="S10" s="2">
+        <v>36</v>
+      </c>
+      <c r="T10" s="2">
+        <v>10</v>
+      </c>
+      <c r="U10" s="2">
+        <v>168</v>
+      </c>
+      <c r="V10" s="2">
+        <v>9</v>
+      </c>
+      <c r="W10" s="2">
+        <v>18</v>
+      </c>
+      <c r="X10" s="2"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2">
+        <v>30</v>
+      </c>
+      <c r="F11" s="2">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2">
+        <v>898</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>76</v>
+      </c>
+      <c r="J11" s="2">
+        <v>18</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11">
+        <v>-3.9</v>
+      </c>
+      <c r="N11" s="11">
+        <v>-7.6</v>
+      </c>
+      <c r="O11" s="2">
+        <v>42</v>
+      </c>
+      <c r="P11" s="2">
+        <v>28</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>23</v>
+      </c>
+      <c r="R11" s="2">
+        <v>9</v>
+      </c>
+      <c r="S11" s="2">
+        <v>56</v>
+      </c>
+      <c r="T11" s="2">
+        <v>7</v>
+      </c>
+      <c r="U11" s="2">
+        <v>294</v>
+      </c>
+      <c r="V11" s="2">
+        <v>13</v>
+      </c>
+      <c r="W11" s="2">
+        <v>26</v>
+      </c>
+      <c r="X11" s="2"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2">
+        <v>57</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>811</v>
+      </c>
+      <c r="H12" s="2">
+        <v>95</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="O12" s="2">
+        <v>32</v>
+      </c>
+      <c r="P12" s="2">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>34</v>
+      </c>
+      <c r="R12" s="2">
+        <v>2</v>
+      </c>
+      <c r="S12" s="2">
+        <v>23</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2">
+        <v>327</v>
+      </c>
+      <c r="V12" s="2">
+        <v>6</v>
+      </c>
+      <c r="W12" s="2">
+        <v>16</v>
+      </c>
+      <c r="X12" s="2"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2">
+        <v>28</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2">
+        <v>705</v>
+      </c>
+      <c r="H13" s="2">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="N13" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="O13" s="2">
+        <v>17</v>
+      </c>
+      <c r="P13" s="2">
+        <v>14</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>24</v>
+      </c>
+      <c r="R13" s="2">
+        <v>3</v>
+      </c>
+      <c r="S13" s="2">
+        <v>33</v>
+      </c>
+      <c r="T13" s="2">
+        <v>12</v>
+      </c>
+      <c r="U13" s="2">
+        <v>358</v>
+      </c>
+      <c r="V13" s="2">
+        <v>6</v>
+      </c>
+      <c r="W13" s="2">
+        <v>11</v>
+      </c>
+      <c r="X13" s="2"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>438</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
+        <v>2</v>
+      </c>
+      <c r="L14" s="2">
+        <v>98</v>
+      </c>
+      <c r="M14" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="N14" s="10">
+        <v>4</v>
+      </c>
+      <c r="O14" s="2">
+        <v>9</v>
+      </c>
+      <c r="P14" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>39</v>
+      </c>
+      <c r="R14" s="2">
+        <v>4</v>
+      </c>
+      <c r="S14" s="2">
+        <v>17</v>
+      </c>
+      <c r="T14" s="2">
+        <v>2</v>
+      </c>
+      <c r="U14" s="2">
+        <v>102</v>
+      </c>
+      <c r="V14" s="2">
+        <v>4</v>
+      </c>
+      <c r="W14" s="2">
+        <v>7</v>
+      </c>
+      <c r="X14" s="2"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2">
+        <v>23</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>219</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2">
+        <v>53</v>
+      </c>
+      <c r="J15" s="2">
+        <v>37</v>
+      </c>
+      <c r="K15" s="2">
+        <v>9</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="10">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N15" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="O15" s="2">
+        <v>4</v>
+      </c>
+      <c r="P15" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>6</v>
+      </c>
+      <c r="R15" s="2">
+        <v>1</v>
+      </c>
+      <c r="S15" s="2">
+        <v>8</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2">
+        <v>58</v>
+      </c>
+      <c r="V15" s="2">
+        <v>2</v>
+      </c>
+      <c r="W15" s="2">
+        <v>5</v>
+      </c>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="2">
+        <v>27</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>123</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>63</v>
+      </c>
+      <c r="J16" s="2">
+        <v>36</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="N16" s="10">
+        <v>11.4</v>
+      </c>
+      <c r="O16" s="2">
+        <v>2</v>
+      </c>
+      <c r="P16" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>4</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2">
+        <v>2</v>
+      </c>
+      <c r="U16" s="2">
+        <v>25</v>
+      </c>
+      <c r="V16" s="2">
+        <v>0</v>
+      </c>
+      <c r="W16" s="2">
+        <v>2</v>
+      </c>
+      <c r="X16" s="2"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2">
+        <v>21</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="2">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>42</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2">
+        <v>100</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N17" s="11">
+        <v>-0.5</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>7</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
+        <v>1</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>17</v>
+      </c>
+      <c r="V17" s="2">
+        <v>0</v>
+      </c>
+      <c r="W17" s="2">
+        <v>0</v>
+      </c>
+      <c r="X17" s="2"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2">
+        <v>23</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2">
+        <v>7</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="11">
+        <v>-22</v>
+      </c>
+      <c r="N18" s="11">
+        <v>-24.1</v>
+      </c>
+      <c r="O18" s="2">
+        <v>1</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>1</v>
+      </c>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <v>1</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>7</v>
+      </c>
+      <c r="V18" s="2">
+        <v>0</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0</v>
+      </c>
+      <c r="X18" s="2"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2">
+        <v>24</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>22</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2">
+        <v>100</v>
+      </c>
+      <c r="M19" s="10">
+        <v>15.9</v>
+      </c>
+      <c r="N19" s="10">
+        <v>14</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2">
+        <v>1</v>
+      </c>
+      <c r="S19" s="2">
+        <v>1</v>
+      </c>
+      <c r="T19" s="2">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2">
+        <v>1</v>
+      </c>
+      <c r="W19" s="2">
+        <v>2</v>
+      </c>
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2">
+        <v>24</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>17</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>95</v>
+      </c>
+      <c r="K20" s="2">
+        <v>5</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="N20" s="11">
+        <v>-1.4</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
+        <v>1</v>
+      </c>
+      <c r="T20" s="2">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2">
+        <v>6</v>
+      </c>
+      <c r="V20" s="2">
+        <v>0</v>
+      </c>
+      <c r="W20" s="2">
+        <v>0</v>
+      </c>
+      <c r="X20" s="2"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="2">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>74</v>
+      </c>
+      <c r="L21" s="2">
+        <v>26</v>
+      </c>
+      <c r="M21" s="10">
+        <v>37</v>
+      </c>
+      <c r="N21" s="10">
+        <v>35.1</v>
+      </c>
+      <c r="O21" s="2">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>1</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2">
+        <v>3</v>
+      </c>
+      <c r="V21" s="2">
+        <v>0</v>
+      </c>
+      <c r="W21" s="2">
+        <v>0</v>
+      </c>
+      <c r="X21" s="2"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2">
+        <v>25</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>4</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>100</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="10">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="N22" s="10">
+        <v>69.5</v>
+      </c>
+      <c r="O22" s="2">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
+        <v>3</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2">
+        <v>0</v>
+      </c>
+      <c r="X22" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.basketball-reference.com/players/c/cunnica01.html" xr:uid="{7693D5F6-2244-EC41-8B23-D3686E0D4067}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.basketball-reference.com/players/h/harrito02.html" xr:uid="{970E9471-05F1-044C-94FA-32ACDE33F00C}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://www.basketball-reference.com/players/b/beaslma01.html" xr:uid="{1AD5C222-5DE7-434A-9848-BA004374C719}"/>
+    <hyperlink ref="X4" r:id="rId4" location="all_smoy" display="https://www.basketball-reference.com/awards/awards_2025.html - all_smoy" xr:uid="{C113ADCE-C700-294B-BB6F-F384D3FAD133}"/>
+    <hyperlink ref="B5" r:id="rId5" display="https://www.basketball-reference.com/players/h/hardati02.html" xr:uid="{61C2FDB3-371F-2E49-8E54-BD19B09011A5}"/>
+    <hyperlink ref="B6" r:id="rId6" display="https://www.basketball-reference.com/players/d/durenja01.html" xr:uid="{F73CEA67-3E45-2441-870F-61DFB7D0AD68}"/>
+    <hyperlink ref="B7" r:id="rId7" display="https://www.basketball-reference.com/players/s/stewais01.html" xr:uid="{FE378F23-0106-0841-BEFF-5643167A4E28}"/>
+    <hyperlink ref="B8" r:id="rId8" display="https://www.basketball-reference.com/players/t/thompau01.html" xr:uid="{C7A07521-4146-B847-B6CF-0E2694FC21B3}"/>
+    <hyperlink ref="B9" r:id="rId9" display="https://www.basketball-reference.com/players/h/hollaro01.html" xr:uid="{D71A0904-620D-D144-8AE0-1DC9F96B9AC3}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://www.basketball-reference.com/players/f/fontesi01.html" xr:uid="{0FD406B9-DF00-2A4E-B8A9-C01B0CC93663}"/>
+    <hyperlink ref="B11" r:id="rId11" display="https://www.basketball-reference.com/players/i/iveyja01.html" xr:uid="{B4A0F9D2-D8A3-754E-9F6F-57E460A3916B}"/>
+    <hyperlink ref="B12" r:id="rId12" display="https://www.basketball-reference.com/players/s/sassema01.html" xr:uid="{13410EC9-1B63-6F4D-9A93-616C5431DF33}"/>
+    <hyperlink ref="B13" r:id="rId13" display="https://www.basketball-reference.com/players/s/schrode01.html" xr:uid="{FE86FB7A-197B-D540-880D-A2DC31CEC3DD}"/>
+    <hyperlink ref="B14" r:id="rId14" display="https://www.basketball-reference.com/players/r/reedpa01.html" xr:uid="{A52D1572-1021-7241-A5AB-0A76E4434717}"/>
+    <hyperlink ref="B15" r:id="rId15" display="https://www.basketball-reference.com/players/m/moorewe01.html" xr:uid="{0E21B540-D30D-BF48-A8B1-4023371C83BA}"/>
+    <hyperlink ref="B16" r:id="rId16" display="https://www.basketball-reference.com/players/w/waterli01.html" xr:uid="{4085B15D-C759-D54B-9FE1-46B8934D2E1A}"/>
+    <hyperlink ref="B17" r:id="rId17" display="https://www.basketball-reference.com/players/k/klintbo01.html" xr:uid="{ECC9BB42-9715-2148-BFC2-DEA6DE80716C}"/>
+    <hyperlink ref="B18" r:id="rId18" display="https://www.basketball-reference.com/players/j/jenkida01.html" xr:uid="{37CB81B3-B7A5-5548-A17A-ADCEAB43B015}"/>
+    <hyperlink ref="B19" r:id="rId19" display="https://www.basketball-reference.com/players/s/smithto05.html" xr:uid="{B98F3A52-A742-5F49-97DE-3C02731C6478}"/>
+    <hyperlink ref="B20" r:id="rId20" display="https://www.basketball-reference.com/players/h/harpero02.html" xr:uid="{DE5D447E-19C2-804C-8842-6359FE079CC3}"/>
+    <hyperlink ref="B21" r:id="rId21" display="https://www.basketball-reference.com/players/s/swideco01.html" xr:uid="{4F96376B-E50B-4842-BF45-6FD89E739BC5}"/>
+    <hyperlink ref="B22" r:id="rId22" display="https://www.basketball-reference.com/players/w/willial06.html" xr:uid="{061C0617-DFBA-924F-AA82-255A0764FF04}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Projects/Pistons_Players_Regular_Season_Data_2024-2025.xlsx
+++ b/Projects/Pistons_Players_Regular_Season_Data_2024-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609354DD-8863-7A46-9CC3-D9ACBEB3EB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0176C2B-BD97-B74E-83A4-3C2FC84B1B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17560" activeTab="9" xr2:uid="{9F5AD747-0CA0-0449-80A8-FFDBC90AA643}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17560" activeTab="8" xr2:uid="{9F5AD747-0CA0-0449-80A8-FFDBC90AA643}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Play-by-Play" sheetId="9" r:id="rId9"/>
     <sheet name="Salaries" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -16073,23 +16073,21 @@
     <col min="5" max="5" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">

--- a/Projects/Pistons_Players_Regular_Season_Data_2024-2025.xlsx
+++ b/Projects/Pistons_Players_Regular_Season_Data_2024-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0176C2B-BD97-B74E-83A4-3C2FC84B1B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC39FF53-5731-E744-B721-8E9D03300A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17560" activeTab="8" xr2:uid="{9F5AD747-0CA0-0449-80A8-FFDBC90AA643}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17560" activeTab="9" xr2:uid="{9F5AD747-0CA0-0449-80A8-FFDBC90AA643}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
